--- a/data/nzd0170/nzd0170.xlsx
+++ b/data/nzd0170/nzd0170.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H382"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11898,6 +11898,126 @@
         <v>353.02</v>
       </c>
       <c r="H382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>330.58</v>
+      </c>
+      <c r="C383" t="n">
+        <v>336.67</v>
+      </c>
+      <c r="D383" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="E383" t="n">
+        <v>349.51</v>
+      </c>
+      <c r="F383" t="n">
+        <v>350.26</v>
+      </c>
+      <c r="G383" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>329.84</v>
+      </c>
+      <c r="C384" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="D384" t="n">
+        <v>344.87</v>
+      </c>
+      <c r="E384" t="n">
+        <v>349.27</v>
+      </c>
+      <c r="F384" t="n">
+        <v>348.98</v>
+      </c>
+      <c r="G384" t="n">
+        <v>350.16</v>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>329.89</v>
+      </c>
+      <c r="C385" t="n">
+        <v>336.29</v>
+      </c>
+      <c r="D385" t="n">
+        <v>345.85</v>
+      </c>
+      <c r="E385" t="n">
+        <v>349.9</v>
+      </c>
+      <c r="F385" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="G385" t="n">
+        <v>350.27</v>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="C386" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="D386" t="n">
+        <v>344.23</v>
+      </c>
+      <c r="E386" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="F386" t="n">
+        <v>350.74</v>
+      </c>
+      <c r="G386" t="n">
+        <v>351.46</v>
+      </c>
+      <c r="H386" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11914,7 +12034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B397"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15887,6 +16007,46 @@
       </c>
       <c r="B397" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -16055,28 +16215,28 @@
         <v>0.1132</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2800894328810278</v>
+        <v>0.2780947555084906</v>
       </c>
       <c r="J2" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1288233517509536</v>
+        <v>0.1297594774461593</v>
       </c>
       <c r="M2" t="n">
-        <v>4.266784202464102</v>
+        <v>4.234415054115883</v>
       </c>
       <c r="N2" t="n">
-        <v>29.76241385161225</v>
+        <v>29.46795924874019</v>
       </c>
       <c r="O2" t="n">
-        <v>5.455493914542684</v>
+        <v>5.428439854022534</v>
       </c>
       <c r="P2" t="n">
-        <v>323.1560666295177</v>
+        <v>323.1775571046456</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16133,28 +16293,28 @@
         <v>0.1448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3575558980070694</v>
+        <v>0.3607429068980454</v>
       </c>
       <c r="J3" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K3" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1108301350421089</v>
+        <v>0.1148536189099886</v>
       </c>
       <c r="M3" t="n">
-        <v>6.170781999699841</v>
+        <v>6.121329417366793</v>
       </c>
       <c r="N3" t="n">
-        <v>57.54105726053503</v>
+        <v>56.98102589677971</v>
       </c>
       <c r="O3" t="n">
-        <v>7.585582196544641</v>
+        <v>7.548577739997099</v>
       </c>
       <c r="P3" t="n">
-        <v>324.311807119448</v>
+        <v>324.277514488022</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16211,28 +16371,28 @@
         <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1920886493180304</v>
+        <v>0.195998710236123</v>
       </c>
       <c r="J4" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05640813927717059</v>
+        <v>0.05981036818118879</v>
       </c>
       <c r="M4" t="n">
-        <v>4.625184474504879</v>
+        <v>4.598232144095088</v>
       </c>
       <c r="N4" t="n">
-        <v>34.62652340183968</v>
+        <v>34.30912621163582</v>
       </c>
       <c r="O4" t="n">
-        <v>5.884430592830515</v>
+        <v>5.857399270293585</v>
       </c>
       <c r="P4" t="n">
-        <v>337.6354062845817</v>
+        <v>337.5933047951403</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16289,28 +16449,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2253169532446877</v>
+        <v>0.2229757351891101</v>
       </c>
       <c r="J5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09674498468541315</v>
+        <v>0.09689306065172476</v>
       </c>
       <c r="M5" t="n">
-        <v>3.792938167238722</v>
+        <v>3.76618717198067</v>
       </c>
       <c r="N5" t="n">
-        <v>26.59088141491675</v>
+        <v>26.32849064398799</v>
       </c>
       <c r="O5" t="n">
-        <v>5.156634698610786</v>
+        <v>5.131129568037431</v>
       </c>
       <c r="P5" t="n">
-        <v>344.6005722149291</v>
+        <v>344.625777832688</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16367,28 +16527,28 @@
         <v>0.1083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3181014096233621</v>
+        <v>0.3209945806828098</v>
       </c>
       <c r="J6" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K6" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L6" t="n">
-        <v>0.142090406025013</v>
+        <v>0.1470986506075271</v>
       </c>
       <c r="M6" t="n">
-        <v>4.71155915976405</v>
+        <v>4.675846917271218</v>
       </c>
       <c r="N6" t="n">
-        <v>34.27449213097842</v>
+        <v>33.94296389417791</v>
       </c>
       <c r="O6" t="n">
-        <v>5.854442085372304</v>
+        <v>5.826059036276401</v>
       </c>
       <c r="P6" t="n">
-        <v>339.9975286500679</v>
+        <v>339.9663732533069</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16445,28 +16605,28 @@
         <v>0.1275</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2231320070209644</v>
+        <v>0.2248535612823549</v>
       </c>
       <c r="J7" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K7" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08820266665504051</v>
+        <v>0.09131204807727533</v>
       </c>
       <c r="M7" t="n">
-        <v>4.373286400106059</v>
+        <v>4.335652012396864</v>
       </c>
       <c r="N7" t="n">
-        <v>28.87376500974932</v>
+        <v>28.5858082140711</v>
       </c>
       <c r="O7" t="n">
-        <v>5.373431399929594</v>
+        <v>5.346569761451833</v>
       </c>
       <c r="P7" t="n">
-        <v>344.0198762715296</v>
+        <v>344.0013427557543</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16504,7 +16664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H382"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32551,6 +32711,174 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-36.772417363192815,175.74873013071647</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-36.773130128651616,175.74859745005284</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-36.77384581701213,175.74847836307103</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-36.77456331295788,175.74834515207627</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-36.775283855510644,175.74824705149373</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-36.7760008887126,175.74817042304142</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-36.772416007141096,175.74872201793082</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-36.77312780137011,175.74858352662946</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-36.77384734161713,175.7484876904203</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-36.77456299603644,175.74834249366558</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-36.775282806298264,175.74823277779535</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-36.77599974714066,175.74815357388397</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-36.772416098766236,175.748722566092</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-36.77312943229984,175.74859328398907</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-36.773849099396074,175.74849844430574</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-36.77456382795506,175.74834947199366</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>-36.775283683374354,175.74824470971507</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>-36.77599983030162,175.74815480130604</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>-36.77241380813713,175.74870886206273</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>-36.77312483270938,175.74856576604324</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-36.773846193679326,175.74848066747492</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-36.77456322052246,175.7483443767065</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>-36.77528424896486,175.74825240413068</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>-36.776000729951086,175.74816807978107</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0170/nzd0170.xlsx
+++ b/data/nzd0170/nzd0170.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12020,6 +12020,36 @@
       <c r="H386" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="C387" t="n">
+        <v>334.84</v>
+      </c>
+      <c r="D387" t="n">
+        <v>345.4</v>
+      </c>
+      <c r="E387" t="n">
+        <v>349.77</v>
+      </c>
+      <c r="F387" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="G387" t="n">
+        <v>351.15</v>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B401"/>
+  <dimension ref="A1:B402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16047,6 +16077,16 @@
       </c>
       <c r="B401" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -16215,28 +16255,28 @@
         <v>0.1132</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2780947555084906</v>
+        <v>0.2773537004430572</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K2" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1297594774461593</v>
+        <v>0.1297767924100619</v>
       </c>
       <c r="M2" t="n">
-        <v>4.234415054115883</v>
+        <v>4.227862845965045</v>
       </c>
       <c r="N2" t="n">
-        <v>29.46795924874019</v>
+        <v>29.39711473968682</v>
       </c>
       <c r="O2" t="n">
-        <v>5.428439854022534</v>
+        <v>5.421910617087562</v>
       </c>
       <c r="P2" t="n">
-        <v>323.1775571046456</v>
+        <v>323.1855541914006</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16293,28 +16333,28 @@
         <v>0.1448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3607429068980454</v>
+        <v>0.3611504346615345</v>
       </c>
       <c r="J3" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K3" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1148536189099886</v>
+        <v>0.1156597939525236</v>
       </c>
       <c r="M3" t="n">
-        <v>6.121329417366793</v>
+        <v>6.107210816663378</v>
       </c>
       <c r="N3" t="n">
-        <v>56.98102589677971</v>
+        <v>56.83506917981483</v>
       </c>
       <c r="O3" t="n">
-        <v>7.548577739997099</v>
+        <v>7.538903712066817</v>
       </c>
       <c r="P3" t="n">
-        <v>324.277514488022</v>
+        <v>324.2731166571026</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16371,28 +16411,28 @@
         <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.195998710236123</v>
+        <v>0.1972654631863498</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05981036818118879</v>
+        <v>0.06083588876883994</v>
       </c>
       <c r="M4" t="n">
-        <v>4.598232144095088</v>
+        <v>4.593193750471216</v>
       </c>
       <c r="N4" t="n">
-        <v>34.30912621163582</v>
+        <v>34.23630583320325</v>
       </c>
       <c r="O4" t="n">
-        <v>5.857399270293585</v>
+        <v>5.851179866762194</v>
       </c>
       <c r="P4" t="n">
-        <v>337.5933047951403</v>
+        <v>337.5796346460344</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16449,28 +16489,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2229757351891101</v>
+        <v>0.2225271490508774</v>
       </c>
       <c r="J5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09689306065172476</v>
+        <v>0.09703075668563232</v>
       </c>
       <c r="M5" t="n">
-        <v>3.76618717198067</v>
+        <v>3.758883162938073</v>
       </c>
       <c r="N5" t="n">
-        <v>26.32849064398799</v>
+        <v>26.2622965132153</v>
       </c>
       <c r="O5" t="n">
-        <v>5.131129568037431</v>
+        <v>5.124675259293539</v>
       </c>
       <c r="P5" t="n">
-        <v>344.625777832688</v>
+        <v>344.6306187445608</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16527,28 +16567,28 @@
         <v>0.1083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3209945806828098</v>
+        <v>0.3224692223619294</v>
       </c>
       <c r="J6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1470986506075271</v>
+        <v>0.1488892745336916</v>
       </c>
       <c r="M6" t="n">
-        <v>4.675846917271218</v>
+        <v>4.670432081741317</v>
       </c>
       <c r="N6" t="n">
-        <v>33.94296389417791</v>
+        <v>33.87679711777897</v>
       </c>
       <c r="O6" t="n">
-        <v>5.826059036276401</v>
+        <v>5.82037774700053</v>
       </c>
       <c r="P6" t="n">
-        <v>339.9663732533069</v>
+        <v>339.9504596755031</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16605,28 +16645,28 @@
         <v>0.1275</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2248535612823549</v>
+        <v>0.2253915079175535</v>
       </c>
       <c r="J7" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K7" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09131204807727533</v>
+        <v>0.09217484957974942</v>
       </c>
       <c r="M7" t="n">
-        <v>4.335652012396864</v>
+        <v>4.326876250003131</v>
       </c>
       <c r="N7" t="n">
-        <v>28.5858082140711</v>
+        <v>28.51464860045341</v>
       </c>
       <c r="O7" t="n">
-        <v>5.346569761451833</v>
+        <v>5.339910916902398</v>
       </c>
       <c r="P7" t="n">
-        <v>344.0013427557543</v>
+        <v>343.9955375111617</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16664,7 +16704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32879,6 +32919,48 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>-36.77241490763931,175.7487154399967</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>-36.7731267751667,175.74857738716742</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-36.77384829225281,175.74849350629705</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-36.774563656289345,175.7483480320212</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-36.7752849211152,175.74826154821892</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>-36.77600049558876,175.74816462068253</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0170/nzd0170.xlsx
+++ b/data/nzd0170/nzd0170.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H387"/>
+  <dimension ref="A1:H388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12050,6 +12050,36 @@
       <c r="H387" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>328.96</v>
+      </c>
+      <c r="C388" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="D388" t="n">
+        <v>348.67</v>
+      </c>
+      <c r="E388" t="n">
+        <v>349.43</v>
+      </c>
+      <c r="F388" t="n">
+        <v>351.64</v>
+      </c>
+      <c r="G388" t="n">
+        <v>350.99</v>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12064,7 +12094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B402"/>
+  <dimension ref="A1:B403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16087,6 +16117,16 @@
       </c>
       <c r="B402" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -16255,28 +16295,28 @@
         <v>0.1132</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2773537004430572</v>
+        <v>0.2764627104990661</v>
       </c>
       <c r="J2" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K2" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1297767924100619</v>
+        <v>0.1296663440150391</v>
       </c>
       <c r="M2" t="n">
-        <v>4.227862845965045</v>
+        <v>4.222195157345324</v>
       </c>
       <c r="N2" t="n">
-        <v>29.39711473968682</v>
+        <v>29.32905605626834</v>
       </c>
       <c r="O2" t="n">
-        <v>5.421910617087562</v>
+        <v>5.415630716386443</v>
       </c>
       <c r="P2" t="n">
-        <v>323.1855541914006</v>
+        <v>323.1952136339364</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16333,28 +16373,28 @@
         <v>0.1448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3611504346615345</v>
+        <v>0.3614917234414661</v>
       </c>
       <c r="J3" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K3" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1156597939525236</v>
+        <v>0.11643891048414</v>
       </c>
       <c r="M3" t="n">
-        <v>6.107210816663378</v>
+        <v>6.09286750989621</v>
       </c>
       <c r="N3" t="n">
-        <v>56.83506917981483</v>
+        <v>56.68936806687846</v>
       </c>
       <c r="O3" t="n">
-        <v>7.538903712066817</v>
+        <v>7.529234228451022</v>
       </c>
       <c r="P3" t="n">
-        <v>324.2731166571026</v>
+        <v>324.2694166609578</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16411,28 +16451,28 @@
         <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1972654631863498</v>
+        <v>0.2001746144820964</v>
       </c>
       <c r="J4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06083588876883994</v>
+        <v>0.06272194044290269</v>
       </c>
       <c r="M4" t="n">
-        <v>4.593193750471216</v>
+        <v>4.596936297459647</v>
       </c>
       <c r="N4" t="n">
-        <v>34.23630583320325</v>
+        <v>34.2320901257316</v>
       </c>
       <c r="O4" t="n">
-        <v>5.851179866762194</v>
+        <v>5.850819611450314</v>
       </c>
       <c r="P4" t="n">
-        <v>337.5796346460344</v>
+        <v>337.5480958167146</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16489,28 +16529,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2225271490508774</v>
+        <v>0.2218980699219459</v>
       </c>
       <c r="J5" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K5" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09703075668563232</v>
+        <v>0.09702322939770092</v>
       </c>
       <c r="M5" t="n">
-        <v>3.758883162938073</v>
+        <v>3.752565244670695</v>
       </c>
       <c r="N5" t="n">
-        <v>26.2622965132153</v>
+        <v>26.19837485238133</v>
       </c>
       <c r="O5" t="n">
-        <v>5.124675259293539</v>
+        <v>5.118434804936108</v>
       </c>
       <c r="P5" t="n">
-        <v>344.6306187445608</v>
+        <v>344.6374387471178</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16567,28 +16607,28 @@
         <v>0.1083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3224692223619294</v>
+        <v>0.3239548416665103</v>
       </c>
       <c r="J6" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K6" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1488892745336916</v>
+        <v>0.1507065675761109</v>
       </c>
       <c r="M6" t="n">
-        <v>4.670432081741317</v>
+        <v>4.665025819872342</v>
       </c>
       <c r="N6" t="n">
-        <v>33.87679711777897</v>
+        <v>33.81123135460894</v>
       </c>
       <c r="O6" t="n">
-        <v>5.82037774700053</v>
+        <v>5.814742587132206</v>
       </c>
       <c r="P6" t="n">
-        <v>339.9504596755031</v>
+        <v>339.9343537088765</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16645,28 +16685,28 @@
         <v>0.1275</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2253915079175535</v>
+        <v>0.2258332824164974</v>
       </c>
       <c r="J7" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K7" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09217484957974942</v>
+        <v>0.09297915250181132</v>
       </c>
       <c r="M7" t="n">
-        <v>4.326876250003131</v>
+        <v>4.317687362777283</v>
       </c>
       <c r="N7" t="n">
-        <v>28.51464860045341</v>
+        <v>28.44291018941313</v>
       </c>
       <c r="O7" t="n">
-        <v>5.339910916902398</v>
+        <v>5.333189494984509</v>
       </c>
       <c r="P7" t="n">
-        <v>343.9955375111617</v>
+        <v>343.9907481244632</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16704,7 +16744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H387"/>
+  <dimension ref="A1:H388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32961,6 +33001,48 @@
         </is>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>-36.77241439453834,175.74871237029416</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>-36.773126610241135,175.74857640046818</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-36.77385415748916,175.7485293891622</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-36.7745632073174,175.74834426593938</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>-36.775284986690814,175.7482624403251</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>-36.77600037462752,175.74816283534133</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
